--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/UTAH_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/UTAH_2015.xlsx
@@ -1903,7 +1903,7 @@
         <v>12</v>
       </c>
       <c r="D86">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="87">
@@ -3937,7 +3937,7 @@
         <v>12</v>
       </c>
       <c r="D199">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="200">
@@ -4603,7 +4603,7 @@
         <v>12</v>
       </c>
       <c r="D236">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="237">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C280">
@@ -5521,7 +5521,7 @@
         <v>12</v>
       </c>
       <c r="D287">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="288">
@@ -7411,7 +7411,7 @@
         <v>12</v>
       </c>
       <c r="D392">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="393">
@@ -11767,7 +11767,7 @@
         <v>12</v>
       </c>
       <c r="D634">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="635">
@@ -12361,7 +12361,7 @@
         <v>12</v>
       </c>
       <c r="D667">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="668">
@@ -12811,7 +12811,7 @@
         <v>12</v>
       </c>
       <c r="D692">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="693">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C772">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C773">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C791">
@@ -15529,7 +15529,7 @@
         <v>12</v>
       </c>
       <c r="D843">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="844">
@@ -15727,7 +15727,7 @@
         <v>12</v>
       </c>
       <c r="D854">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="855">
@@ -16429,7 +16429,7 @@
         <v>12</v>
       </c>
       <c r="D893">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="894">
@@ -18589,7 +18589,7 @@
         <v>12</v>
       </c>
       <c r="D1013">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="1014">
@@ -18877,7 +18877,7 @@
         <v>12</v>
       </c>
       <c r="D1029">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="1030">
@@ -20731,7 +20731,7 @@
         <v>12</v>
       </c>
       <c r="D1132">
-        <v>0.0009405125793557489</v>
+        <v>0.0009405125793557488</v>
       </c>
     </row>
     <row r="1133">
